--- a/packages/filesv2/src/assets/templates/empty.xlsx
+++ b/packages/filesv2/src/assets/templates/empty.xlsx
@@ -221,7 +221,7 @@
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;12Page &amp;P</oddFooter>
